--- a/trunk/recursos/formatos_layout/formato_layout_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
+++ b/trunk/recursos/formatos_layout/formato_layout_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
@@ -13,7 +13,6 @@
   </bookViews>
   <sheets>
     <sheet name="Oficios" sheetId="1" r:id="rId1"/>
-    <sheet name="Prioridad" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
-  <si>
-    <t>NUM. OFICIOS</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>FECHA OFICIO</t>
   </si>
@@ -45,38 +41,26 @@
     <t>Obligatorio</t>
   </si>
   <si>
-    <t>PRIORIDAD</t>
-  </si>
-  <si>
-    <t>CODIGO</t>
-  </si>
-  <si>
-    <t>DESCRIPCION</t>
-  </si>
-  <si>
-    <t>NIVEL_A</t>
-  </si>
-  <si>
-    <t>NIVEL_B</t>
-  </si>
-  <si>
-    <t>NIVEL_C</t>
-  </si>
-  <si>
-    <t>Nivel A</t>
-  </si>
-  <si>
-    <t>Nivel B</t>
-  </si>
-  <si>
-    <t>Nivel C</t>
+    <t>NUM. ORDEN</t>
+  </si>
+  <si>
+    <t>NUM. OFICIO</t>
+  </si>
+  <si>
+    <t>ID BLOQUE</t>
+  </si>
+  <si>
+    <t>ID INSUMO</t>
+  </si>
+  <si>
+    <t>MONTO PRESUNTIVA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,21 +78,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri Light"/>
       <family val="2"/>
@@ -166,67 +135,15 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Calibri Light"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Calibri Light"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Calibri Light"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Calibri Light"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -237,17 +154,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:B4"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="CODIGO" dataDxfId="3"/>
-    <tableColumn id="2" name="DESCRIPCION" dataDxfId="2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,101 +419,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="17.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="35" style="2" customWidth="1"/>
-    <col min="5" max="5" width="48" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="17.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35" style="2" customWidth="1"/>
+    <col min="8" max="8" width="48" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>